--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-13T00:31:13+00:00</t>
+          <t>2026-09-14T00:33:52+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-14T00:33:52+00:00</t>
+          <t>2026-09-15T01:07:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15T01:07:10+00:00</t>
+          <t>2026-09-16T00:55:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-16T00:55:19+00:00</t>
+          <t>2026-09-24T01:01:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-24T01:01:40+00:00</t>
+          <t>2026-09-25T01:03:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-25T01:03:14+00:00</t>
+          <t>2026-09-26T01:06:00+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-26T01:06:00+00:00</t>
+          <t>2026-09-27T01:03:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-27T01:03:28+00:00</t>
+          <t>2026-09-28T01:22:16+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-28T01:22:16+00:00</t>
+          <t>2026-09-29T02:27:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29T02:27:10+00:00</t>
+          <t>2026-09-30T01:46:22+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-30T01:46:22+00:00</t>
+          <t>2026-10-01T01:44:44+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-01T01:44:44+00:00</t>
+          <t>2026-10-02T01:54:48+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02T01:54:48+00:00</t>
+          <t>2026-10-03T01:37:49+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-03T01:37:49+00:00</t>
+          <t>2026-10-04T02:18:17+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-04T02:18:17+00:00</t>
+          <t>2026-10-05T01:26:50+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-05T01:26:50+00:00</t>
+          <t>2026-10-06T02:37:35+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06T02:37:35+00:00</t>
+          <t>2026-10-07T01:55:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-07T01:55:53+00:00</t>
+          <t>2026-10-08T02:24:00+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08T02:24:00+00:00</t>
+          <t>2026-10-09T02:42:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-09T02:42:19+00:00</t>
+          <t>2026-10-10T02:01:47+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-10T02:01:47+00:00</t>
+          <t>2026-10-10T09:16:27+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-10T09:16:27+00:00</t>
+          <t>2026-10-10T16:04:12+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-10T16:04:12+00:00</t>
+          <t>2026-10-10T22:08:54+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-10T22:08:54+00:00</t>
+          <t>2026-10-11T01:26:47+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-11T01:26:47+00:00</t>
+          <t>2026-10-11T09:33:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-11T09:33:36+00:00</t>
+          <t>2026-10-11T16:29:57+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-11T16:29:57+00:00</t>
+          <t>2026-10-11T22:37:38+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-11T22:37:38+00:00</t>
+          <t>2026-10-12T01:57:16+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-12T01:57:16+00:00</t>
+          <t>2026-10-12T10:03:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-12T10:03:33+00:00</t>
+          <t>2026-10-12T20:05:32+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-12T20:05:32+00:00</t>
+          <t>2026-10-13T03:18:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-13T03:18:56+00:00</t>
+          <t>2026-10-13T14:44:01+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-13T14:44:01+00:00</t>
+          <t>2026-10-13T20:29:02+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-13T20:29:02+00:00</t>
+          <t>2026-10-14T01:31:24+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14T01:31:24+00:00</t>
+          <t>2026-10-14T08:16:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14T08:16:19+00:00</t>
+          <t>2026-10-14T15:40:27+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14T15:40:27+00:00</t>
+          <t>2026-10-14T22:00:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14T22:00:56+00:00</t>
+          <t>2026-10-15T01:09:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-15T01:09:40+00:00</t>
+          <t>2026-10-15T07:53:55+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-15T07:53:55+00:00</t>
+          <t>2026-10-15T15:26:47+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-15T15:26:47+00:00</t>
+          <t>2026-10-15T21:54:35+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-15T21:54:35+00:00</t>
+          <t>2026-10-16T00:56:23+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16T00:56:23+00:00</t>
+          <t>2026-10-16T07:45:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16T07:45:28+00:00</t>
+          <t>2026-10-16T15:06:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16T15:06:25+00:00</t>
+          <t>2026-10-16T21:52:31+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16T21:52:31+00:00</t>
+          <t>2026-10-17T00:56:37+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T00:56:37+00:00</t>
+          <t>2026-10-17T07:22:47+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T07:22:47+00:00</t>
+          <t>2026-10-17T14:02:52+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T14:02:52+00:00</t>
+          <t>2026-10-17T17:42:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T17:42:18+00:00</t>
+          <t>2026-10-17T21:11:17+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T21:11:17+00:00</t>
+          <t>2026-10-18T00:31:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T00:31:53+00:00</t>
+          <t>2026-10-18T07:36:55+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T07:36:55+00:00</t>
+          <t>2026-10-18T14:14:54+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T14:14:54+00:00</t>
+          <t>2026-10-18T17:43:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T17:43:14+00:00</t>
+          <t>2026-10-18T21:13:20+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T21:13:20+00:00</t>
+          <t>2026-10-19T00:38:42+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19T00:38:42+00:00</t>
+          <t>2026-10-19T08:20:48+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19T08:20:48+00:00</t>
+          <t>2026-10-19T17:18:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19T17:18:11+00:00</t>
+          <t>2026-10-19T22:43:34+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19T22:43:34+00:00</t>
+          <t>2026-10-20T01:23:44+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20T01:23:44+00:00</t>
+          <t>2026-10-20T08:04:52+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20T08:04:52+00:00</t>
+          <t>2026-10-20T15:31:12+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20T15:31:12+00:00</t>
+          <t>2026-10-20T22:01:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20T22:01:25+00:00</t>
+          <t>2026-10-21T01:10:29+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21T01:10:29+00:00</t>
+          <t>2026-10-21T08:10:17+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21T08:10:17+00:00</t>
+          <t>2026-10-21T15:47:08+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21T15:47:08+00:00</t>
+          <t>2026-10-21T22:04:09+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21T22:04:09+00:00</t>
+          <t>2026-10-22T01:07:16+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-22T01:07:16+00:00</t>
+          <t>2026-10-22T08:10:24+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-22T08:10:24+00:00</t>
+          <t>2026-10-22T15:46:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-22T15:46:14+00:00</t>
+          <t>2026-10-22T22:01:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-22T22:01:28+00:00</t>
+          <t>2026-10-23T01:08:12+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-23T01:08:12+00:00</t>
+          <t>2026-10-23T08:09:07+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-23T08:09:07+00:00</t>
+          <t>2026-10-23T15:34:21+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-23T15:34:21+00:00</t>
+          <t>2026-10-23T21:49:08+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-23T21:49:08+00:00</t>
+          <t>2026-10-24T01:17:17+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T01:17:17+00:00</t>
+          <t>2026-10-24T07:47:39+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T07:47:39+00:00</t>
+          <t>2026-10-24T09:10:05+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T09:10:05+00:00</t>
+          <t>2026-10-24T14:12:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T14:12:36+00:00</t>
+          <t>2026-10-24T15:23:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T15:23:14+00:00</t>
+          <t>2026-10-24T17:44:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T17:44:40+00:00</t>
+          <t>2026-10-24T21:21:15+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T21:21:15+00:00</t>
+          <t>2026-10-25T00:43:04+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T00:43:04+00:00</t>
+          <t>2026-10-25T07:57:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T07:57:53+00:00</t>
+          <t>2026-10-25T14:43:09+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T14:43:09+00:00</t>
+          <t>2026-10-25T18:00:59+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T18:00:59+00:00</t>
+          <t>2026-10-25T21:26:02+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T21:26:02+00:00</t>
+          <t>2026-10-26T00:57:22+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T00:57:22+00:00</t>
+          <t>2026-10-26T08:29:13+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T08:29:13+00:00</t>
+          <t>2026-10-26T17:05:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T17:05:25+00:00</t>
+          <t>2026-10-26T22:58:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T22:58:18+00:00</t>
+          <t>2026-10-27T01:45:06+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T01:45:06+00:00</t>
+          <t>2026-10-27T01:48:13+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T01:48:13+00:00</t>
+          <t>2026-10-27T08:32:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T08:32:11+00:00</t>
+          <t>2026-10-27T16:08:26+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T16:08:26+00:00</t>
+          <t>2026-10-27T22:47:12+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T22:47:12+00:00</t>
+          <t>2026-10-28T01:56:32+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T01:56:32+00:00</t>
+          <t>2026-10-28T09:11:39+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T09:11:39+00:00</t>
+          <t>2026-10-28T16:56:04+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T16:56:04+00:00</t>
+          <t>2026-10-28T22:55:55+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T22:55:55+00:00</t>
+          <t>2026-10-29T02:01:22+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T02:01:22+00:00</t>
+          <t>2026-10-29T06:41:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T06:41:33+00:00</t>
+          <t>2026-10-29T09:09:37+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T09:09:37+00:00</t>
+          <t>2026-10-29T17:13:38+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T17:13:38+00:00</t>
+          <t>2026-10-29T23:04:01+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T23:04:01+00:00</t>
+          <t>2026-10-30T02:17:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T02:17:18+00:00</t>
+          <t>2026-10-30T09:20:37+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T09:20:37+00:00</t>
+          <t>2026-10-30T16:54:49+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T16:54:49+00:00</t>
+          <t>2026-10-30T22:45:09+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T22:45:09+00:00</t>
+          <t>2026-10-31T01:56:30+00:00</t>
         </is>
       </c>
     </row>
